--- a/trenes/backend/google-sheet-template-trenes.xlsx
+++ b/trenes/backend/google-sheet-template-trenes.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrdenesTrenes" sheetId="1" r:id="R9f32245785924ff7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PasajerosTren" sheetId="2" r:id="R81c04acdeb024847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PagosTren" sheetId="3" r:id="R0f1503627875431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LogsTren" sheetId="4" r:id="R094bf904e1024d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="5" r:id="Ra71a3630b85b46d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoExtras" sheetId="6" r:id="R1ac2294b8af246ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrdenesTrenes" sheetId="1" r:id="R5538e253fcc44c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PasajerosTren" sheetId="2" r:id="R0eb071102bf645e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PagosTren" sheetId="3" r:id="R60c5c97c8cab4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LogsTren" sheetId="4" r:id="Ra8bcc257329843aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="5" r:id="R99abeee0b5f147b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoExtras" sheetId="6" r:id="Rc7015fc48e754bb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,6 +45,11 @@
         <x:fgColor rgb="062803"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="0A3A26"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -53,7 +58,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -73,6 +78,18 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -407,46 +424,50 @@
     <x:col min="7" max="7" width="10.359999656677246" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.789999961853027" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="15.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="4.039999961853027" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="7.940000057220459" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="5.25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.859999656677246" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="4.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="7.940000057220459" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="5.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>fechaRegistro</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>codigoReserva</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>indice</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>tipo</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>nombres</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>apellidos</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>nacionalidad</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="16" t="str">
         <x:v>tipoDocumento</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="16" t="str">
         <x:v>numeroDocumento</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="16" t="str">
+        <x:v>fechaNacimiento</x:v>
+      </x:c>
+      <x:c r="K1" s="16" t="str">
         <x:v>edad</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="L1" s="16" t="str">
         <x:v>whatsapp</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="M1" s="16" t="str">
         <x:v>correo</x:v>
       </x:c>
     </x:row>

--- a/trenes/backend/google-sheet-template-trenes.xlsx
+++ b/trenes/backend/google-sheet-template-trenes.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrdenesTrenes" sheetId="1" r:id="R5538e253fcc44c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PasajerosTren" sheetId="2" r:id="R0eb071102bf645e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PagosTren" sheetId="3" r:id="R60c5c97c8cab4311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LogsTren" sheetId="4" r:id="Ra8bcc257329843aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="5" r:id="R99abeee0b5f147b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoExtras" sheetId="6" r:id="Rc7015fc48e754bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OrdenesTrenes" sheetId="1" r:id="R9f32245785924ff7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PasajerosTren" sheetId="2" r:id="R81c04acdeb024847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PagosTren" sheetId="3" r:id="R0f1503627875431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LogsTren" sheetId="4" r:id="R094bf904e1024d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="5" r:id="Ra71a3630b85b46d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoExtras" sheetId="6" r:id="R1ac2294b8af246ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +33,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,11 +45,6 @@
         <x:fgColor rgb="062803"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="0A3A26"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -58,7 +53,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -78,18 +73,6 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -424,50 +407,46 @@
     <x:col min="7" max="7" width="10.359999656677246" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.789999961853027" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="15.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.859999656677246" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="4.039999961853027" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="7.940000057220459" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="5.25" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="4.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7.940000057220459" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="5.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>fechaRegistro</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>codigoReserva</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>indice</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>tipo</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>nombres</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>apellidos</x:v>
       </x:c>
-      <x:c r="G1" s="16" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>nacionalidad</x:v>
       </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>tipoDocumento</x:v>
       </x:c>
-      <x:c r="I1" s="16" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>numeroDocumento</x:v>
       </x:c>
-      <x:c r="J1" s="16" t="str">
-        <x:v>fechaNacimiento</x:v>
-      </x:c>
-      <x:c r="K1" s="16" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>edad</x:v>
       </x:c>
-      <x:c r="L1" s="16" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>whatsapp</x:v>
       </x:c>
-      <x:c r="M1" s="16" t="str">
+      <x:c r="L1" s="5" t="str">
         <x:v>correo</x:v>
       </x:c>
     </x:row>
